--- a/log_analysis/triage_tool/error_db.xlsx
+++ b/log_analysis/triage_tool/error_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,6 @@
           <t>DUT Bug</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>tc_sanity</t>
@@ -537,6 +536,30 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UVM_ERROR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>test cause</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>

--- a/log_analysis/triage_tool/error_db.xlsx
+++ b/log_analysis/triage_tool/error_db.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误知识库" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="错误知识库" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,7 @@
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,6 +492,11 @@
           <t>录入日期</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>稳定ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -538,6 +544,11 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7f2e16bbfa96</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -545,21 +556,19 @@
           <t>UVM_ERROR</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>test cause</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6af14585a7b3</t>
         </is>
       </c>
     </row>
